--- a/UTCUTS/A1_Inputs/A-I_Classifier_Modes_Supply.xlsx
+++ b/UTCUTS/A1_Inputs/A-I_Classifier_Modes_Supply.xlsx
@@ -5113,7 +5113,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBF1B2B7-8260-46AE-9509-16F7A00FBC72}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5784D256-80D1-43B5-8E19-CDB4AC90D4A0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
